--- a/diseases/d106/1975-1979.xlsx
+++ b/diseases/d106/1975-1979.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">

--- a/diseases/d106/1975-1979.xlsx
+++ b/diseases/d106/1975-1979.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
